--- a/datatables/sysaudit_trail/SAT-APR-2026_19-May-2026 09-17-18 UTC+0.xlsx
+++ b/datatables/sysaudit_trail/SAT-APR-2026_19-May-2026 09-17-18 UTC+0.xlsx
@@ -12483,4 +12483,10 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{c5e6e129-f928-4a05-ae32-d838f6b21bdd}" enabled="1" method="Standard" siteId="{8b87af7d-8647-4dc7-8df4-5f69a2011bb5}" contentBits="3" removed="0"/>
+</clbl:labelList>
 </file>